--- a/DummyDataInput.xlsx
+++ b/DummyDataInput.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JFairouz\Documents\PythonHosting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65396636-12E3-49EC-BFA0-5FCF70C3310C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A405E036-68DF-4ACC-8268-F0A95B0CE3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4004" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4004" uniqueCount="441">
   <si>
     <t>Merk</t>
   </si>
@@ -1345,6 +1345,9 @@
   </si>
   <si>
     <t>Originele Omschrijving</t>
+  </si>
+  <si>
+    <t>HamerWRONG</t>
   </si>
 </sst>
 </file>
@@ -1741,7 +1744,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>440</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
